--- a/initial_data.xlsx
+++ b/initial_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,22 +513,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NYX_A001</t>
+          <t>LDR0-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -562,7 +562,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>centering</t>
@@ -587,7 +591,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -597,12 +601,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NYX_A002</t>
+          <t>LDR0-2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -636,7 +640,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>centering</t>
@@ -661,22 +669,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NYX_A003</t>
+          <t>LDR0-3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -710,7 +718,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>centering</t>
@@ -735,22 +747,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NYX_A004</t>
+          <t>LDR0-4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -784,7 +796,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>centering</t>
@@ -809,22 +825,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NYX_A005</t>
+          <t>LDR0-5_001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -858,7 +874,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>centering</t>
@@ -883,22 +903,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NYX_A006</t>
+          <t>LDR0-5_002</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -932,7 +952,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>centering</t>
@@ -957,22 +981,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NYX_A007</t>
+          <t>LDR0-7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1006,7 +1030,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1031,22 +1059,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NYX_A008</t>
+          <t>LDR0-8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1080,7 +1108,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1105,22 +1137,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NYX_A009</t>
+          <t>LDR0-9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1154,7 +1186,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1179,22 +1215,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NYX_A010</t>
+          <t>LDR0-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1228,7 +1264,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1253,22 +1293,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NYX_A011</t>
+          <t>LDR0-11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1302,7 +1342,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1327,22 +1371,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>LDR0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NYX_A012</t>
+          <t>LDR0-12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1376,7 +1420,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1401,22 +1449,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NYX_A013</t>
+          <t>CWA2-1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1450,7 +1498,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1475,22 +1527,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NYX_A014</t>
+          <t>CWA2-2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1524,7 +1576,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1549,22 +1605,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NYX_A015</t>
+          <t>CWA2-3_001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1598,7 +1654,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1623,22 +1683,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0000_NYX_01</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NYX_A016</t>
+          <t>CWA2-3_002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1672,7 +1732,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1697,22 +1761,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NYX_B001</t>
+          <t>CWA2-5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1746,7 +1810,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1771,22 +1839,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NYX_B002</t>
+          <t>CWA2-6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1820,7 +1888,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1845,22 +1917,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYX_B003</t>
+          <t>CWA2-7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1894,7 +1966,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1919,22 +1995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NYX_B004</t>
+          <t>CWA2-8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1968,7 +2044,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>centering</t>
@@ -1993,22 +2073,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYX_B005</t>
+          <t>CWA2-9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2042,7 +2122,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2067,22 +2151,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>CWA2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYX_B006</t>
+          <t>CWA2-10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2116,7 +2200,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2141,22 +2229,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NYX_B007</t>
+          <t>PQz9-1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2190,7 +2278,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2215,22 +2307,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NYX_B008</t>
+          <t>PQZ9-2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -2264,7 +2356,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2289,22 +2385,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYX_B009</t>
+          <t>PQZ9-3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2338,7 +2434,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2363,22 +2463,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYX_B010</t>
+          <t>PQZ9-4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -2412,7 +2512,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2437,22 +2541,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYX_B011</t>
+          <t>PQZ9-5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2486,7 +2590,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2511,22 +2619,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYX_B012</t>
+          <t>PQZ9-6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2560,7 +2668,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2585,22 +2697,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>PQZ9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYX_B013</t>
+          <t>PQZ9-7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -2634,7 +2746,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2659,22 +2775,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYX_B014</t>
+          <t>WWG8-1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2708,7 +2824,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2733,22 +2853,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYX_B015</t>
+          <t>WWG8-2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2782,7 +2902,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2807,22 +2931,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0000_NYX_02</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYX_B016</t>
+          <t>WWG8-3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2856,7 +2980,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2881,22 +3009,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYX_C001</t>
+          <t>WWG8-4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2930,7 +3058,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>centering</t>
@@ -2955,22 +3087,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYX_C002</t>
+          <t>WWG8-5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3004,7 +3136,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3029,22 +3165,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYX_C003</t>
+          <t>WWG8-6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -3078,7 +3214,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3103,22 +3243,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYX_C004</t>
+          <t>WWG5-1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -3152,7 +3292,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3177,22 +3321,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NYX_C005</t>
+          <t>WWG5-2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -3226,7 +3370,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3251,22 +3399,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NYX_C006</t>
+          <t>WWG5-3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3300,7 +3448,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3325,22 +3477,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NYX_C007</t>
+          <t>WWG5-4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3374,7 +3526,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3399,22 +3555,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NYX_C008</t>
+          <t>WWG5-5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3448,7 +3604,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3473,22 +3633,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>WWG5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NYX_C009</t>
+          <t>WWG5-6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3522,7 +3682,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3547,22 +3711,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NYX_C010</t>
+          <t>QWEQ-1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3596,7 +3760,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3621,22 +3789,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NYX_C011</t>
+          <t>QWEQ-2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3670,7 +3838,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3695,22 +3867,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NYX_C012</t>
+          <t>QWEQ-3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3744,7 +3916,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3769,22 +3945,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NYX_C013</t>
+          <t>QWEQ-4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3818,7 +3994,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3843,22 +4023,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NYX_C014</t>
+          <t>QWEQ-5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3892,7 +4072,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3917,22 +4101,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NYX_C015</t>
+          <t>QWEQ-6</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3966,7 +4150,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>centering</t>
@@ -3991,22 +4179,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0000_NYX_03</t>
+          <t>QWEQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NYX_C016</t>
+          <t>QWEQ-7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>310208</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -4040,7 +4228,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>centering</t>
@@ -4057,6 +4249,240 @@
         </is>
       </c>
       <c r="P49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QWEQ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QWEQ-8</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>310208</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>centering</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QWEQ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>QWEQ-9</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>310208</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>centering</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QWEQ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>QWEQ-10</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>310208</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>centering</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
